--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.05497</v>
+        <v>17.09007</v>
       </c>
       <c r="D2" t="n">
-        <v>16.79474</v>
+        <v>16.53382</v>
       </c>
       <c r="E2" t="n">
-        <v>17.17448</v>
+        <v>16.693</v>
       </c>
       <c r="F2" t="n">
-        <v>42.02983</v>
+        <v>43.20072</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05046</v>
+        <v>0.04998</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84607</v>
+        <v>1.80981</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.77497</v>
+        <v>17.154</v>
       </c>
       <c r="D3" t="n">
-        <v>16.8977</v>
+        <v>16.54302</v>
       </c>
       <c r="E3" t="n">
-        <v>16.26041</v>
+        <v>16.97353</v>
       </c>
       <c r="F3" t="n">
-        <v>43.123</v>
+        <v>42.41722</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05152</v>
+        <v>0.05165</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8296</v>
+        <v>1.81976</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.95712</v>
+        <v>16.90773</v>
       </c>
       <c r="D4" t="n">
-        <v>17.01484</v>
+        <v>16.31421</v>
       </c>
       <c r="E4" t="n">
-        <v>16.42065</v>
+        <v>16.44522</v>
       </c>
       <c r="F4" t="n">
-        <v>42.52641</v>
+        <v>43.09381</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0501</v>
+        <v>0.05188</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81373</v>
+        <v>1.81608</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.72118</v>
+        <v>17.17448</v>
       </c>
       <c r="D5" t="n">
-        <v>16.6078</v>
+        <v>16.79474</v>
       </c>
       <c r="E5" t="n">
-        <v>16.74132</v>
+        <v>17.05497</v>
       </c>
       <c r="F5" t="n">
-        <v>42.87171</v>
+        <v>42.02983</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05107</v>
+        <v>0.05046</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82598</v>
+        <v>1.84607</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.61088</v>
+        <v>16.8977</v>
       </c>
       <c r="D6" t="n">
-        <v>17.00276</v>
+        <v>16.26041</v>
       </c>
       <c r="E6" t="n">
-        <v>16.80259</v>
+        <v>16.77497</v>
       </c>
       <c r="F6" t="n">
-        <v>42.31338</v>
+        <v>43.123</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05048</v>
+        <v>0.05152</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82094</v>
+        <v>1.8296</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.03331</v>
+        <v>17.01484</v>
       </c>
       <c r="D7" t="n">
-        <v>16.73692</v>
+        <v>16.42065</v>
       </c>
       <c r="E7" t="n">
-        <v>16.83743</v>
+        <v>16.95712</v>
       </c>
       <c r="F7" t="n">
-        <v>43.74095</v>
+        <v>42.52641</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05116</v>
+        <v>0.0501</v>
       </c>
       <c r="H7" t="n">
-        <v>1.78068</v>
+        <v>1.81373</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.13084</v>
+        <v>16.74132</v>
       </c>
       <c r="D8" t="n">
-        <v>16.87886</v>
+        <v>16.6078</v>
       </c>
       <c r="E8" t="n">
-        <v>16.50539</v>
+        <v>16.72118</v>
       </c>
       <c r="F8" t="n">
-        <v>43.24238</v>
+        <v>42.87171</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05101</v>
+        <v>0.05107</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83435</v>
+        <v>1.82598</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.02908</v>
+        <v>17.00276</v>
       </c>
       <c r="D9" t="n">
-        <v>16.63328</v>
+        <v>16.61088</v>
       </c>
       <c r="E9" t="n">
-        <v>16.62851</v>
+        <v>16.80259</v>
       </c>
       <c r="F9" t="n">
-        <v>42.29686</v>
+        <v>42.31338</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05082</v>
+        <v>0.05048</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82192</v>
+        <v>1.82094</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.61372</v>
+        <v>17.03331</v>
       </c>
       <c r="D10" t="n">
-        <v>16.34549</v>
+        <v>16.73692</v>
       </c>
       <c r="E10" t="n">
-        <v>16.37003</v>
+        <v>16.83743</v>
       </c>
       <c r="F10" t="n">
-        <v>41.44314</v>
+        <v>43.74095</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05225</v>
+        <v>0.05116</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85755</v>
+        <v>1.78068</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.913</v>
+        <v>17.13084</v>
       </c>
       <c r="D12" t="n">
-        <v>16.52045</v>
+        <v>16.50539</v>
       </c>
       <c r="E12" t="n">
-        <v>16.30719</v>
+        <v>16.87886</v>
       </c>
       <c r="F12" t="n">
-        <v>42.84888</v>
+        <v>43.24238</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05151</v>
+        <v>0.05101</v>
       </c>
       <c r="H12" t="n">
-        <v>1.83062</v>
+        <v>1.83435</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.71544</v>
+        <v>17.02908</v>
       </c>
       <c r="D13" t="n">
-        <v>16.76913</v>
+        <v>16.62851</v>
       </c>
       <c r="E13" t="n">
-        <v>16.56971</v>
+        <v>16.63328</v>
       </c>
       <c r="F13" t="n">
-        <v>42.6759</v>
+        <v>42.29686</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05044</v>
+        <v>0.05082</v>
       </c>
       <c r="H13" t="n">
-        <v>1.80077</v>
+        <v>1.82192</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.24976</v>
+        <v>16.61372</v>
       </c>
       <c r="D14" t="n">
-        <v>16.93203</v>
+        <v>16.34549</v>
       </c>
       <c r="E14" t="n">
-        <v>16.72464</v>
+        <v>16.37003</v>
       </c>
       <c r="F14" t="n">
-        <v>43.32155</v>
+        <v>41.44314</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05107</v>
+        <v>0.05225</v>
       </c>
       <c r="H14" t="n">
-        <v>1.84342</v>
+        <v>1.85755</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.05708</v>
+        <v>16.913</v>
       </c>
       <c r="D15" t="n">
-        <v>16.81264</v>
+        <v>16.30719</v>
       </c>
       <c r="E15" t="n">
-        <v>16.40654</v>
+        <v>16.52045</v>
       </c>
       <c r="F15" t="n">
-        <v>43.0256</v>
+        <v>42.84888</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05106</v>
+        <v>0.05151</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8731</v>
+        <v>1.83062</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.6601</v>
+        <v>16.76913</v>
       </c>
       <c r="D16" t="n">
-        <v>16.9082</v>
+        <v>16.56971</v>
       </c>
       <c r="E16" t="n">
-        <v>16.7994</v>
+        <v>16.71544</v>
       </c>
       <c r="F16" t="n">
-        <v>42.89815</v>
+        <v>42.6759</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05162</v>
+        <v>0.05044</v>
       </c>
       <c r="H16" t="n">
-        <v>1.82116</v>
+        <v>1.80077</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.25852</v>
+        <v>17.24976</v>
       </c>
       <c r="D17" t="n">
-        <v>16.65004</v>
+        <v>16.72464</v>
       </c>
       <c r="E17" t="n">
-        <v>16.89708</v>
+        <v>16.93203</v>
       </c>
       <c r="F17" t="n">
-        <v>42.18292</v>
+        <v>43.32155</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05127</v>
+        <v>0.05107</v>
       </c>
       <c r="H17" t="n">
-        <v>1.85436</v>
+        <v>1.84342</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.21246</v>
+        <v>17.05708</v>
       </c>
       <c r="D18" t="n">
-        <v>17.01176</v>
+        <v>16.40654</v>
       </c>
       <c r="E18" t="n">
-        <v>16.51868</v>
+        <v>16.81264</v>
       </c>
       <c r="F18" t="n">
-        <v>42.34537</v>
+        <v>43.0256</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0507</v>
+        <v>0.05106</v>
       </c>
       <c r="H18" t="n">
-        <v>1.83617</v>
+        <v>1.8731</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.13299</v>
+        <v>16.9082</v>
       </c>
       <c r="D19" t="n">
-        <v>16.74434</v>
+        <v>16.6601</v>
       </c>
       <c r="E19" t="n">
-        <v>16.77628</v>
+        <v>16.7994</v>
       </c>
       <c r="F19" t="n">
-        <v>42.49867</v>
+        <v>42.89815</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05066</v>
+        <v>0.05162</v>
       </c>
       <c r="H19" t="n">
-        <v>1.81787</v>
+        <v>1.82116</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.12961</v>
+        <v>17.25852</v>
       </c>
       <c r="D20" t="n">
-        <v>16.80178</v>
+        <v>16.65004</v>
       </c>
       <c r="E20" t="n">
-        <v>16.76161</v>
+        <v>16.89708</v>
       </c>
       <c r="F20" t="n">
-        <v>41.84046</v>
+        <v>42.18292</v>
       </c>
       <c r="G20" t="n">
-        <v>0.04922</v>
+        <v>0.05127</v>
       </c>
       <c r="H20" t="n">
-        <v>1.79347</v>
+        <v>1.85436</v>
       </c>
     </row>
     <row r="21">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.61032</v>
+        <v>16.07188</v>
       </c>
       <c r="D22" t="n">
-        <v>15.83311</v>
+        <v>15.46749</v>
       </c>
       <c r="E22" t="n">
-        <v>15.6237</v>
+        <v>15.97446</v>
       </c>
       <c r="F22" t="n">
-        <v>253.11668</v>
+        <v>253.46726</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.11942</v>
+        <v>15.94607</v>
       </c>
       <c r="D23" t="n">
-        <v>15.62834</v>
+        <v>15.70949</v>
       </c>
       <c r="E23" t="n">
-        <v>15.56464</v>
+        <v>15.71739</v>
       </c>
       <c r="F23" t="n">
-        <v>254.32852</v>
+        <v>256.67851</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.90056</v>
+        <v>15.75953</v>
       </c>
       <c r="D24" t="n">
-        <v>15.43671</v>
+        <v>15.58285</v>
       </c>
       <c r="E24" t="n">
-        <v>15.71753</v>
+        <v>15.6532</v>
       </c>
       <c r="F24" t="n">
-        <v>253.80003</v>
+        <v>253.89622</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.8708</v>
+        <v>15.99452</v>
       </c>
       <c r="D25" t="n">
-        <v>15.85643</v>
+        <v>15.69496</v>
       </c>
       <c r="E25" t="n">
-        <v>15.51956</v>
+        <v>15.77728</v>
       </c>
       <c r="F25" t="n">
-        <v>259.06713</v>
+        <v>250.44504</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.56023</v>
+        <v>15.55996</v>
       </c>
       <c r="D26" t="n">
-        <v>15.61262</v>
+        <v>15.25688</v>
       </c>
       <c r="E26" t="n">
-        <v>15.60584</v>
+        <v>15.34414</v>
       </c>
       <c r="F26" t="n">
-        <v>254.40752</v>
+        <v>258.47044</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.74187</v>
+        <v>16.06743</v>
       </c>
       <c r="D27" t="n">
-        <v>15.61989</v>
+        <v>15.50516</v>
       </c>
       <c r="E27" t="n">
-        <v>15.9756</v>
+        <v>15.67426</v>
       </c>
       <c r="F27" t="n">
-        <v>259.22775</v>
+        <v>255.1275</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.82196</v>
+        <v>15.84927</v>
       </c>
       <c r="D28" t="n">
-        <v>15.51136</v>
+        <v>15.57939</v>
       </c>
       <c r="E28" t="n">
-        <v>15.73191</v>
+        <v>15.61501</v>
       </c>
       <c r="F28" t="n">
-        <v>256.98882</v>
+        <v>251.99922</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.69585</v>
+        <v>15.81961</v>
       </c>
       <c r="D29" t="n">
-        <v>16.16444</v>
+        <v>15.54702</v>
       </c>
       <c r="E29" t="n">
-        <v>15.80565</v>
+        <v>15.76839</v>
       </c>
       <c r="F29" t="n">
-        <v>254.05696</v>
+        <v>258.85108</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.30249</v>
+        <v>15.86967</v>
       </c>
       <c r="D30" t="n">
-        <v>15.65168</v>
+        <v>15.51004</v>
       </c>
       <c r="E30" t="n">
-        <v>15.63209</v>
+        <v>15.56978</v>
       </c>
       <c r="F30" t="n">
-        <v>254.16116</v>
+        <v>254.87089</v>
       </c>
     </row>
     <row r="31">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.64254</v>
+        <v>16.66643</v>
       </c>
       <c r="D32" t="n">
-        <v>16.05358</v>
+        <v>15.98902</v>
       </c>
       <c r="E32" t="n">
-        <v>16.70789</v>
+        <v>16.4528</v>
       </c>
       <c r="F32" t="n">
-        <v>22.13543</v>
+        <v>21.80698</v>
       </c>
       <c r="G32" t="n">
-        <v>34.64282</v>
+        <v>34.94986</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.81033</v>
+        <v>17.01375</v>
       </c>
       <c r="D33" t="n">
-        <v>15.83128</v>
+        <v>16.12819</v>
       </c>
       <c r="E33" t="n">
-        <v>16.73434</v>
+        <v>16.31715</v>
       </c>
       <c r="F33" t="n">
-        <v>21.84346</v>
+        <v>21.89231</v>
       </c>
       <c r="G33" t="n">
-        <v>34.71158</v>
+        <v>34.5514</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.85336</v>
+        <v>16.70848</v>
       </c>
       <c r="D34" t="n">
-        <v>16.21822</v>
+        <v>16.57291</v>
       </c>
       <c r="E34" t="n">
-        <v>16.07032</v>
+        <v>16.5843</v>
       </c>
       <c r="F34" t="n">
-        <v>21.83273</v>
+        <v>21.72723</v>
       </c>
       <c r="G34" t="n">
-        <v>34.76127</v>
+        <v>33.36931</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.82917</v>
+        <v>16.76966</v>
       </c>
       <c r="D35" t="n">
-        <v>15.93755</v>
+        <v>15.98622</v>
       </c>
       <c r="E35" t="n">
-        <v>16.52929</v>
+        <v>16.37793</v>
       </c>
       <c r="F35" t="n">
-        <v>21.57852</v>
+        <v>21.68574</v>
       </c>
       <c r="G35" t="n">
-        <v>33.91104</v>
+        <v>34.34246</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.95947</v>
+        <v>17.0173</v>
       </c>
       <c r="D36" t="n">
-        <v>16.18837</v>
+        <v>16.26697</v>
       </c>
       <c r="E36" t="n">
-        <v>16.24992</v>
+        <v>16.60395</v>
       </c>
       <c r="F36" t="n">
-        <v>22.05341</v>
+        <v>21.90436</v>
       </c>
       <c r="G36" t="n">
-        <v>33.92216</v>
+        <v>33.86692</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.63895</v>
+        <v>17.04424</v>
       </c>
       <c r="D37" t="n">
-        <v>15.86691</v>
+        <v>16.05241</v>
       </c>
       <c r="E37" t="n">
-        <v>16.46399</v>
+        <v>16.63691</v>
       </c>
       <c r="F37" t="n">
-        <v>22.24914</v>
+        <v>21.96044</v>
       </c>
       <c r="G37" t="n">
-        <v>34.1771</v>
+        <v>34.69467</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.85883</v>
+        <v>16.66072</v>
       </c>
       <c r="D38" t="n">
-        <v>16.16642</v>
+        <v>16.04452</v>
       </c>
       <c r="E38" t="n">
-        <v>16.51877</v>
+        <v>16.36792</v>
       </c>
       <c r="F38" t="n">
-        <v>21.71364</v>
+        <v>21.92891</v>
       </c>
       <c r="G38" t="n">
-        <v>34.70959</v>
+        <v>34.09426</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.44565</v>
+        <v>16.83539</v>
       </c>
       <c r="D39" t="n">
-        <v>16.1615</v>
+        <v>15.8577</v>
       </c>
       <c r="E39" t="n">
-        <v>15.87707</v>
+        <v>16.25322</v>
       </c>
       <c r="F39" t="n">
-        <v>21.96574</v>
+        <v>22.0987</v>
       </c>
       <c r="G39" t="n">
-        <v>34.8079</v>
+        <v>34.63082</v>
       </c>
     </row>
     <row r="40">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.48591</v>
+        <v>16.55084</v>
       </c>
       <c r="D40" t="n">
-        <v>15.99526</v>
+        <v>16.20669</v>
       </c>
       <c r="E40" t="n">
-        <v>16.26978</v>
+        <v>16.25855</v>
       </c>
       <c r="F40" t="n">
-        <v>21.82133</v>
+        <v>21.68105</v>
       </c>
       <c r="G40" t="n">
-        <v>34.39854</v>
+        <v>33.94313</v>
       </c>
     </row>
     <row r="41">
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16.63428</v>
+        <v>16.76888</v>
       </c>
       <c r="D42" t="n">
-        <v>15.75916</v>
+        <v>16.35053</v>
       </c>
       <c r="E42" t="n">
-        <v>16.61923</v>
+        <v>16.38074</v>
       </c>
       <c r="F42" t="n">
-        <v>21.94038</v>
+        <v>21.96757</v>
       </c>
       <c r="G42" t="n">
-        <v>34.25641</v>
+        <v>34.58387</v>
       </c>
     </row>
     <row r="43">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.45043</v>
+        <v>16.82467</v>
       </c>
       <c r="D43" t="n">
-        <v>16.41639</v>
+        <v>15.957</v>
       </c>
       <c r="E43" t="n">
-        <v>16.42016</v>
+        <v>16.63596</v>
       </c>
       <c r="F43" t="n">
-        <v>22.36377</v>
+        <v>21.42918</v>
       </c>
       <c r="G43" t="n">
-        <v>34.55361</v>
+        <v>34.57334</v>
       </c>
     </row>
     <row r="44">
@@ -1451,19 +1451,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.88216</v>
+        <v>16.68308</v>
       </c>
       <c r="D44" t="n">
-        <v>16.0625</v>
+        <v>16.14227</v>
       </c>
       <c r="E44" t="n">
-        <v>16.52644</v>
+        <v>16.17109</v>
       </c>
       <c r="F44" t="n">
-        <v>21.71167</v>
+        <v>21.48164</v>
       </c>
       <c r="G44" t="n">
-        <v>34.06432</v>
+        <v>34.21772</v>
       </c>
     </row>
     <row r="45">
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.72724</v>
+        <v>16.57107</v>
       </c>
       <c r="D45" t="n">
-        <v>15.71929</v>
+        <v>16.03614</v>
       </c>
       <c r="E45" t="n">
-        <v>16.55473</v>
+        <v>16.48687</v>
       </c>
       <c r="F45" t="n">
-        <v>21.77151</v>
+        <v>21.67497</v>
       </c>
       <c r="G45" t="n">
-        <v>34.05574</v>
+        <v>33.71263</v>
       </c>
     </row>
     <row r="46">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.70044</v>
+        <v>16.927</v>
       </c>
       <c r="D46" t="n">
-        <v>15.97275</v>
+        <v>16.12363</v>
       </c>
       <c r="E46" t="n">
-        <v>16.60348</v>
+        <v>16.41875</v>
       </c>
       <c r="F46" t="n">
-        <v>22.03576</v>
+        <v>21.43542</v>
       </c>
       <c r="G46" t="n">
-        <v>35.12516</v>
+        <v>35.11861</v>
       </c>
     </row>
     <row r="47">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.62996</v>
+        <v>16.72424</v>
       </c>
       <c r="D47" t="n">
-        <v>16.24004</v>
+        <v>16.43477</v>
       </c>
       <c r="E47" t="n">
-        <v>16.35401</v>
+        <v>16.5612</v>
       </c>
       <c r="F47" t="n">
-        <v>21.47854</v>
+        <v>21.99797</v>
       </c>
       <c r="G47" t="n">
-        <v>34.12193</v>
+        <v>34.36156</v>
       </c>
     </row>
     <row r="48">
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.74127</v>
+        <v>16.83248</v>
       </c>
       <c r="D48" t="n">
-        <v>16.18232</v>
+        <v>15.95555</v>
       </c>
       <c r="E48" t="n">
-        <v>16.70438</v>
+        <v>16.32669</v>
       </c>
       <c r="F48" t="n">
-        <v>21.92397</v>
+        <v>21.79609</v>
       </c>
       <c r="G48" t="n">
-        <v>34.32525</v>
+        <v>33.62734</v>
       </c>
     </row>
     <row r="49">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.91706</v>
+        <v>16.8613</v>
       </c>
       <c r="D49" t="n">
-        <v>15.79079</v>
+        <v>15.99953</v>
       </c>
       <c r="E49" t="n">
-        <v>16.363</v>
+        <v>16.32257</v>
       </c>
       <c r="F49" t="n">
-        <v>21.84455</v>
+        <v>21.76118</v>
       </c>
       <c r="G49" t="n">
-        <v>33.65045</v>
+        <v>34.16955</v>
       </c>
     </row>
     <row r="50">
@@ -1583,19 +1583,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16.48814</v>
+        <v>16.91095</v>
       </c>
       <c r="D50" t="n">
-        <v>16.23742</v>
+        <v>16.19372</v>
       </c>
       <c r="E50" t="n">
-        <v>16.67397</v>
+        <v>16.83514</v>
       </c>
       <c r="F50" t="n">
-        <v>22.14904</v>
+        <v>21.66934</v>
       </c>
       <c r="G50" t="n">
-        <v>33.92331</v>
+        <v>34.74136</v>
       </c>
     </row>
     <row r="51">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.61409</v>
+        <v>0.6057</v>
       </c>
       <c r="D52" t="n">
-        <v>1.14053</v>
+        <v>1.0989</v>
       </c>
     </row>
     <row r="53">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.59862</v>
+        <v>0.60571</v>
       </c>
       <c r="D53" t="n">
-        <v>1.11994</v>
+        <v>1.11608</v>
       </c>
     </row>
     <row r="54">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.61304</v>
+        <v>0.61452</v>
       </c>
       <c r="D54" t="n">
-        <v>1.1278</v>
+        <v>1.13425</v>
       </c>
     </row>
     <row r="55">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.61714</v>
+        <v>0.61183</v>
       </c>
       <c r="D55" t="n">
-        <v>1.1166</v>
+        <v>1.11709</v>
       </c>
     </row>
     <row r="56">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.61588</v>
+        <v>0.61517</v>
       </c>
       <c r="D56" t="n">
-        <v>1.11546</v>
+        <v>1.09936</v>
       </c>
     </row>
     <row r="57">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.62339</v>
+        <v>0.60604</v>
       </c>
       <c r="D57" t="n">
-        <v>1.10553</v>
+        <v>1.11763</v>
       </c>
     </row>
     <row r="58">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.6069600000000001</v>
+        <v>0.59735</v>
       </c>
       <c r="D58" t="n">
-        <v>1.12589</v>
+        <v>1.09921</v>
       </c>
     </row>
     <row r="59">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.61468</v>
+        <v>0.61661</v>
       </c>
       <c r="D59" t="n">
-        <v>1.1098</v>
+        <v>1.13218</v>
       </c>
     </row>
     <row r="60">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.62823</v>
+        <v>0.61811</v>
       </c>
       <c r="D60" t="n">
-        <v>1.12319</v>
+        <v>1.10401</v>
       </c>
     </row>
     <row r="61">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.60386</v>
+        <v>0.61409</v>
       </c>
       <c r="D62" t="n">
-        <v>1.10014</v>
+        <v>1.14053</v>
       </c>
     </row>
     <row r="63">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.60495</v>
+        <v>0.59862</v>
       </c>
       <c r="D63" t="n">
-        <v>1.10677</v>
+        <v>1.11994</v>
       </c>
     </row>
     <row r="64">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.61134</v>
+        <v>0.61304</v>
       </c>
       <c r="D64" t="n">
-        <v>1.09934</v>
+        <v>1.1278</v>
       </c>
     </row>
     <row r="65">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.62176</v>
+        <v>0.61714</v>
       </c>
       <c r="D65" t="n">
-        <v>1.12333</v>
+        <v>1.1166</v>
       </c>
     </row>
     <row r="66">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.60456</v>
+        <v>0.61588</v>
       </c>
       <c r="D66" t="n">
-        <v>1.10858</v>
+        <v>1.11546</v>
       </c>
     </row>
     <row r="67">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.59522</v>
+        <v>0.62339</v>
       </c>
       <c r="D67" t="n">
-        <v>1.12435</v>
+        <v>1.10553</v>
       </c>
     </row>
     <row r="68">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.60507</v>
+        <v>0.6069600000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>1.11677</v>
+        <v>1.12589</v>
       </c>
     </row>
     <row r="69">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.61125</v>
+        <v>0.61468</v>
       </c>
       <c r="D69" t="n">
-        <v>1.1176</v>
+        <v>1.1098</v>
       </c>
     </row>
     <row r="70">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.60364</v>
+        <v>0.62823</v>
       </c>
       <c r="D70" t="n">
-        <v>1.13904</v>
+        <v>1.12319</v>
       </c>
     </row>
   </sheetData>
